--- a/product_selector_out/STM32H523-533.xlsx
+++ b/product_selector_out/STM32H523-533.xlsx
@@ -6576,9 +6576,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -6913,9 +6913,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -7250,9 +7250,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -7587,9 +7587,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -7924,9 +7924,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -8261,9 +8261,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -8598,9 +8598,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -8935,9 +8935,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -9272,9 +9272,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -9609,9 +9609,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -9946,9 +9946,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -10283,9 +10283,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -10620,9 +10620,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -10957,9 +10957,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -11063,7 +11063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11156,19 +11156,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11222,19 +11222,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11244,19 +11244,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11288,19 +11288,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11310,19 +11310,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11332,19 +11332,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11354,19 +11354,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11376,19 +11376,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11398,19 +11398,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11420,19 +11420,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11464,19 +11464,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11486,19 +11486,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11508,19 +11508,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists WLCSP39 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11552,19 +11552,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11574,19 +11574,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11596,19 +11596,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11618,14 +11618,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11640,19 +11640,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11662,19 +11662,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11684,19 +11684,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11706,14 +11706,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11728,14 +11728,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11757,7 +11757,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11772,29 +11772,337 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>STM32H523ZC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 2. STM32H523xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 19. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>STM32H533ZE</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H523-533.xlsx
+++ b/product_selector_out/STM32H523-533.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1093,7 +1099,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -1430,7 +1436,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1767,7 +1773,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2104,7 +2110,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2778,7 +2784,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -4126,7 +4132,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -4463,7 +4469,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -4800,7 +4806,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -5137,7 +5143,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -6416,14 +6422,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
@@ -6431,9 +6437,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
@@ -6461,9 +6467,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -6753,14 +6759,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
@@ -6768,9 +6774,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
@@ -6798,9 +6804,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -7090,14 +7096,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
@@ -7105,9 +7111,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
@@ -7135,9 +7141,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -7427,14 +7433,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T15" s="7" t="inlineStr">
@@ -7442,9 +7448,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
@@ -7472,9 +7478,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -8101,14 +8107,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
@@ -8116,9 +8122,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
@@ -8146,9 +8152,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -9449,14 +9455,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr">
@@ -9464,9 +9470,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
@@ -9494,9 +9500,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="6" t="inlineStr">
@@ -9786,14 +9792,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T22" s="7" t="inlineStr">
@@ -9801,9 +9807,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
@@ -9831,9 +9837,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="6" t="inlineStr">
@@ -10123,14 +10129,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
@@ -10138,9 +10144,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
@@ -10168,9 +10174,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="6" t="inlineStr">
@@ -10460,14 +10466,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
@@ -10475,9 +10481,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
@@ -10505,9 +10511,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="6" t="inlineStr">

--- a/product_selector_out/STM32H523-533.xlsx
+++ b/product_selector_out/STM32H523-533.xlsx
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN12" s="4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN14" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AM15" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN15" s="4" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AM17" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN17" s="4" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AM21" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN21" s="4" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AM22" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN22" s="4" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AM23" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN23" s="4" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AM24" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN24" s="4" t="inlineStr">
@@ -6527,9 +6527,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -6864,9 +6864,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -7201,9 +7201,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -7538,9 +7538,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -8212,9 +8212,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -9560,9 +9560,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -9897,9 +9897,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -10234,9 +10234,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -10571,9 +10571,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">

--- a/product_selector_out/STM32H523-533.xlsx
+++ b/product_selector_out/STM32H523-533.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO25"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.69140625" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h523cc.pdf</t>
         </is>
       </c>
@@ -5725,12 +5797,17 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h533ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5753,12 +5830,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5773,9 +5852,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -5825,7 +5903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO25"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5895,6 +5973,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6238,6 +6317,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6335,6 +6419,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6667,7 +6752,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7004,7 +7094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7341,7 +7436,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7678,7 +7778,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8015,7 +8120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8352,7 +8462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8689,7 +8804,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9026,7 +9146,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9363,7 +9488,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9700,7 +9830,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10037,7 +10172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10374,7 +10514,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10711,7 +10856,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11048,7 +11198,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11056,8 +11211,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
